--- a/weibull_vs_pareto_results.xlsx
+++ b/weibull_vs_pareto_results.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.95</v>
+        <v>4.015</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4</v>
+        <v>3.472</v>
       </c>
       <c r="E4" t="n">
-        <v>3.487</v>
+        <v>3.591</v>
       </c>
       <c r="F4" t="n">
-        <v>4.896</v>
+        <v>4.921</v>
       </c>
       <c r="G4" t="n">
-        <v>14.326</v>
+        <v>12.166</v>
       </c>
     </row>
     <row r="5">
